--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-specimen.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-specimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-10T06:36:19+00:00</t>
+    <t>2026-08-28T11:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4032,7 +4032,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>202</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>212</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>257</v>
       </c>
@@ -5356,7 +5356,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>279</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>289</v>
       </c>
@@ -6024,7 +6024,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>291</v>
       </c>
@@ -6355,7 +6355,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>294</v>
       </c>
@@ -11191,12 +11191,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AM84">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-specimen.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-specimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T11:20:46+00:00</t>
+    <t>2026-08-28T12:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-specimen.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-specimen.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:05:03+00:00</t>
+    <t>2026-08-28T12:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>83</v>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-specimen.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:17:39+00:00</t>
+    <t>2026-08-31T14:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
